--- a/data/trans_dic/P64D$bicicleta_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 13,52</t>
+          <t>0,19; 15,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,42</t>
+          <t>0,1; 7,25</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 58,67</t>
+          <t>0,23; 61,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 39,42</t>
+          <t>0,49; 35,98</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,52</t>
+          <t>0,54; 2,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,35</t>
+          <t>0,36; 2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,0</t>
+          <t>0,61; 2,01</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,56</t>
+          <t>0,38; 2,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,75</t>
+          <t>0,31; 1,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,94</t>
+          <t>0,52; 1,86</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,16</t>
+          <t>0,31; 2,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,77</t>
+          <t>0,21; 1,75</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,15</t>
+          <t>0,0; 17,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 8,07</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,9</t>
+          <t>0,77; 1,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 20,62</t>
+          <t>0,54; 20,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,62</t>
+          <t>0,92; 11,01</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>162; 12255</t>
+          <t>172; 13680</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2727</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167; 11035</t>
+          <t>173; 12455</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 13828</t>
+          <t>0; 15149</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>826; 205182</t>
+          <t>810; 215953</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3460; 275999</t>
+          <t>3428; 251899</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2113; 11658</t>
+          <t>2488; 13037</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1340; 8254</t>
+          <t>1260; 8394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4904; 16278</t>
+          <t>4934; 16345</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2894; 19111</t>
+          <t>2816; 18377</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1423; 7943</t>
+          <t>1399; 7892</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6604; 23253</t>
+          <t>6257; 22334</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>924; 9461</t>
+          <t>913; 7461</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3950</t>
+          <t>0; 3612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1101; 9004</t>
+          <t>1089; 8888</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3413</t>
+          <t>0; 2943</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 892</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3489</t>
+          <t>0; 2799</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14805; 37416</t>
+          <t>15077; 38597</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8516; 301237</t>
+          <t>7930; 299486</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31321; 398185</t>
+          <t>31386; 377216</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$bicicleta_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Edad-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 15,1</t>
+          <t>2,25; 24,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,25</t>
+          <t>1,19; 13,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 61,75</t>
+          <t>0,59; 3,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 35,98</t>
+          <t>0,43; 2,83</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,82</t>
+          <t>0,81; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,39</t>
+          <t>0,59; 2,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,01</t>
+          <t>0,89; 2,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,47</t>
+          <t>1,23; 4,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,74</t>
+          <t>0,46; 2,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,86</t>
+          <t>1,12; 2,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,49</t>
+          <t>0,29; 2,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,75</t>
+          <t>0,26; 1,71</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,37</t>
+          <t>0,0; 18,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,07</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,96</t>
+          <t>1,25; 2,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 20,5</t>
+          <t>0,69; 1,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 11,01</t>
+          <t>1,19; 2,23</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>9327</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>172; 13680</t>
+          <t>2359; 25664</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173; 12455</t>
+          <t>2330; 27506</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74322</t>
+          <t>8387</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 15149</t>
+          <t>0; 18422</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>810; 215953</t>
+          <t>1856; 10455</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3428; 251899</t>
+          <t>3025; 20111</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>14906</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2488; 13037</t>
+          <t>4342; 17853</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1260; 8394</t>
+          <t>2330; 10415</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4934; 16345</t>
+          <t>8278; 24198</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>17633</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2816; 18377</t>
+          <t>6690; 22280</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1399; 7892</t>
+          <t>2078; 9316</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6257; 22334</t>
+          <t>11156; 27820</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>4336</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>913; 7461</t>
+          <t>943; 7655</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 5047</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1089; 8888</t>
+          <t>1441; 9594</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2943</t>
+          <t>0; 3456</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2799</t>
+          <t>0; 3257</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15077; 38597</t>
+          <t>24122; 56489</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7930; 299486</t>
+          <t>10425; 24974</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31386; 377216</t>
+          <t>40842; 76760</t>
         </is>
       </c>
     </row>
